--- a/FMR_Complete_Dashboard.xlsx
+++ b/FMR_Complete_Dashboard.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Outputs Per Epoch" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epoch 0 vs 50" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Read + FMR Layers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Tracking Layer" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Read Feature Track" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -204,8 +206,53 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -276,6 +323,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+        <bgColor rgb="00B4C6E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -568,6 +621,62 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -36149,4 +36258,7276 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AS55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="28" min="1" max="1"/>
+    <col width="9" customWidth="1" style="28" min="2" max="2"/>
+    <col width="9" customWidth="1" style="28" min="3" max="3"/>
+    <col width="9" customWidth="1" style="28" min="4" max="4"/>
+    <col width="9" customWidth="1" style="28" min="5" max="5"/>
+    <col width="9" customWidth="1" style="28" min="6" max="6"/>
+    <col width="9" customWidth="1" style="28" min="7" max="7"/>
+    <col width="9" customWidth="1" style="28" min="8" max="8"/>
+    <col width="9" customWidth="1" style="28" min="9" max="9"/>
+    <col width="9" customWidth="1" style="28" min="10" max="10"/>
+    <col width="9" customWidth="1" style="28" min="11" max="11"/>
+    <col width="9" customWidth="1" style="28" min="12" max="12"/>
+    <col width="9" customWidth="1" style="28" min="13" max="13"/>
+    <col width="9" customWidth="1" style="28" min="14" max="14"/>
+    <col width="9" customWidth="1" style="28" min="15" max="15"/>
+    <col width="9" customWidth="1" style="28" min="16" max="16"/>
+    <col width="9" customWidth="1" style="28" min="17" max="17"/>
+    <col width="9" customWidth="1" style="28" min="18" max="18"/>
+    <col width="9" customWidth="1" style="28" min="19" max="19"/>
+    <col width="9" customWidth="1" style="28" min="20" max="20"/>
+    <col width="9" customWidth="1" style="28" min="21" max="21"/>
+    <col width="9" customWidth="1" style="28" min="22" max="22"/>
+    <col width="9" customWidth="1" style="28" min="23" max="23"/>
+    <col width="9" customWidth="1" style="28" min="24" max="24"/>
+    <col width="9" customWidth="1" style="28" min="25" max="25"/>
+    <col width="9" customWidth="1" style="28" min="26" max="26"/>
+    <col width="9" customWidth="1" style="28" min="27" max="27"/>
+    <col width="9" customWidth="1" style="28" min="28" max="28"/>
+    <col width="9" customWidth="1" style="28" min="29" max="29"/>
+    <col width="9" customWidth="1" style="28" min="30" max="30"/>
+    <col width="9" customWidth="1" style="28" min="31" max="31"/>
+    <col width="9" customWidth="1" style="28" min="32" max="32"/>
+    <col width="9" customWidth="1" style="28" min="33" max="33"/>
+    <col width="9" customWidth="1" style="28" min="34" max="34"/>
+    <col width="9" customWidth="1" style="28" min="35" max="35"/>
+    <col width="9" customWidth="1" style="28" min="36" max="36"/>
+    <col width="9" customWidth="1" style="28" min="37" max="37"/>
+    <col width="9" customWidth="1" style="28" min="38" max="38"/>
+    <col width="9" customWidth="1" style="28" min="39" max="39"/>
+    <col width="9" customWidth="1" style="28" min="40" max="40"/>
+    <col width="9" customWidth="1" style="28" min="41" max="41"/>
+    <col width="9" customWidth="1" style="28" min="42" max="42"/>
+    <col width="9" customWidth="1" style="28" min="43" max="43"/>
+    <col width="9" customWidth="1" style="28" min="44" max="44"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>Tracking Specific Features Through ResNet-50 Layers Across Epochs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>Each cell = how strongly a specific concept activates at a specific layer. RED=biased GREEN=uniform. Watch f_sky drop &amp; f_beak rise at late layers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1" s="28">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Epoch</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Conv1</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Stage1</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Stage2</t>
+        </is>
+      </c>
+      <c r="E4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Stage3</t>
+        </is>
+      </c>
+      <c r="F4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Stage4</t>
+        </is>
+      </c>
+      <c r="G4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Flatten</t>
+        </is>
+      </c>
+      <c r="H4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@FMR_Applied</t>
+        </is>
+      </c>
+      <c r="I4" s="71" t="inlineStr">
+        <is>
+          <t>f_sky
+@Post_FMR</t>
+        </is>
+      </c>
+      <c r="J4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Conv1</t>
+        </is>
+      </c>
+      <c r="K4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Stage1</t>
+        </is>
+      </c>
+      <c r="L4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Stage2</t>
+        </is>
+      </c>
+      <c r="M4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Stage3</t>
+        </is>
+      </c>
+      <c r="N4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Stage4</t>
+        </is>
+      </c>
+      <c r="O4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Flatten</t>
+        </is>
+      </c>
+      <c r="P4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@FMR_Applied</t>
+        </is>
+      </c>
+      <c r="Q4" s="72" t="inlineStr">
+        <is>
+          <t>f_beak
+@Post_FMR</t>
+        </is>
+      </c>
+      <c r="R4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Conv1</t>
+        </is>
+      </c>
+      <c r="S4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Stage1</t>
+        </is>
+      </c>
+      <c r="T4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Stage2</t>
+        </is>
+      </c>
+      <c r="U4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Stage3</t>
+        </is>
+      </c>
+      <c r="V4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Stage4</t>
+        </is>
+      </c>
+      <c r="W4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Flatten</t>
+        </is>
+      </c>
+      <c r="X4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@FMR_Applied</t>
+        </is>
+      </c>
+      <c r="Y4" s="71" t="inlineStr">
+        <is>
+          <t>f_grass
+@Post_FMR</t>
+        </is>
+      </c>
+      <c r="Z4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Conv1</t>
+        </is>
+      </c>
+      <c r="AA4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Stage1</t>
+        </is>
+      </c>
+      <c r="AB4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Stage2</t>
+        </is>
+      </c>
+      <c r="AC4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Stage3</t>
+        </is>
+      </c>
+      <c r="AD4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Stage4</t>
+        </is>
+      </c>
+      <c r="AE4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Flatten</t>
+        </is>
+      </c>
+      <c r="AF4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@FMR_Applied</t>
+        </is>
+      </c>
+      <c r="AG4" s="73" t="inlineStr">
+        <is>
+          <t>f_wing
+@Post_FMR</t>
+        </is>
+      </c>
+      <c r="AH4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Conv1</t>
+        </is>
+      </c>
+      <c r="AI4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Stage1</t>
+        </is>
+      </c>
+      <c r="AJ4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Stage2</t>
+        </is>
+      </c>
+      <c r="AK4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Stage3</t>
+        </is>
+      </c>
+      <c r="AL4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Stage4</t>
+        </is>
+      </c>
+      <c r="AM4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Flatten</t>
+        </is>
+      </c>
+      <c r="AN4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@FMR_Applied</t>
+        </is>
+      </c>
+      <c r="AO4" s="71" t="inlineStr">
+        <is>
+          <t>f_branch
+@Post_FMR</t>
+        </is>
+      </c>
+      <c r="AP4" s="74" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="AQ4" s="75" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="C5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q5" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="S5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="V5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="W5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="X5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Y5" s="77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Z5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AA5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AD5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AE5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AF5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG5" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AH5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AI5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AK5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AL5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AM5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AN5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO5" s="77" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP5" s="78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ5" s="79" t="n">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="77" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="C6" s="77" t="n">
+        <v>0.8768</v>
+      </c>
+      <c r="D6" s="77" t="n">
+        <v>0.8827</v>
+      </c>
+      <c r="E6" s="77" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="F6" s="77" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="G6" s="77" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="H6" s="77" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="I6" s="77" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="J6" s="77" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="K6" s="77" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="L6" s="77" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="M6" s="77" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="N6" s="77" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="O6" s="77" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="P6" s="77" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="Q6" s="77" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="R6" s="77" t="n">
+        <v>0.8456</v>
+      </c>
+      <c r="S6" s="77" t="n">
+        <v>0.8493000000000001</v>
+      </c>
+      <c r="T6" s="77" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="U6" s="77" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="V6" s="77" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="W6" s="77" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="X6" s="77" t="n">
+        <v>0.8782</v>
+      </c>
+      <c r="Y6" s="77" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="Z6" s="77" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="AA6" s="77" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="AB6" s="77" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="AC6" s="77" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="AD6" s="77" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AE6" s="77" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="AF6" s="77" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="AG6" s="77" t="n">
+        <v>0.2227</v>
+      </c>
+      <c r="AH6" s="77" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="AI6" s="77" t="n">
+        <v>0.7114</v>
+      </c>
+      <c r="AJ6" s="77" t="n">
+        <v>0.7147</v>
+      </c>
+      <c r="AK6" s="77" t="n">
+        <v>0.7191</v>
+      </c>
+      <c r="AL6" s="77" t="n">
+        <v>0.7234</v>
+      </c>
+      <c r="AM6" s="77" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="AN6" s="77" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="AO6" s="77" t="n">
+        <v>0.7278</v>
+      </c>
+      <c r="AP6" s="78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AQ6" s="79" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="77" t="n">
+        <v>0.8394</v>
+      </c>
+      <c r="C7" s="77" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="D7" s="77" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="E7" s="77" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="F7" s="77" t="n">
+        <v>0.8877</v>
+      </c>
+      <c r="G7" s="77" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="H7" s="77" t="n">
+        <v>0.9063</v>
+      </c>
+      <c r="I7" s="77" t="n">
+        <v>0.9026</v>
+      </c>
+      <c r="J7" s="77" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="K7" s="77" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="L7" s="77" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="M7" s="77" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="N7" s="77" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="O7" s="77" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="P7" s="77" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="Q7" s="77" t="n">
+        <v>0.1269</v>
+      </c>
+      <c r="R7" s="77" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="S7" s="77" t="n">
+        <v>0.8215</v>
+      </c>
+      <c r="T7" s="77" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="U7" s="77" t="n">
+        <v>0.8456</v>
+      </c>
+      <c r="V7" s="77" t="n">
+        <v>0.8593</v>
+      </c>
+      <c r="W7" s="77" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="X7" s="77" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="Y7" s="77" t="n">
+        <v>0.8731</v>
+      </c>
+      <c r="Z7" s="77" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="AA7" s="77" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AB7" s="77" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AC7" s="77" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="AD7" s="77" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="AE7" s="77" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AF7" s="77" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="AG7" s="77" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="AH7" s="77" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="AI7" s="77" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="AJ7" s="77" t="n">
+        <v>0.7008</v>
+      </c>
+      <c r="AK7" s="77" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="AL7" s="77" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="AM7" s="77" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="AN7" s="77" t="n">
+        <v>0.7279</v>
+      </c>
+      <c r="AO7" s="77" t="n">
+        <v>0.7258</v>
+      </c>
+      <c r="AP7" s="78" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AQ7" s="79" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="77" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="C8" s="77" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="D8" s="77" t="n">
+        <v>0.8356</v>
+      </c>
+      <c r="E8" s="77" t="n">
+        <v>0.8569</v>
+      </c>
+      <c r="F8" s="77" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="G8" s="77" t="n">
+        <v>0.8834</v>
+      </c>
+      <c r="H8" s="77" t="n">
+        <v>0.9046999999999999</v>
+      </c>
+      <c r="I8" s="77" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="J8" s="77" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="K8" s="77" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="L8" s="77" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="M8" s="77" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="N8" s="77" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="O8" s="77" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="P8" s="77" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="Q8" s="77" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="R8" s="77" t="n">
+        <v>0.7864</v>
+      </c>
+      <c r="S8" s="77" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="T8" s="77" t="n">
+        <v>0.8111</v>
+      </c>
+      <c r="U8" s="77" t="n">
+        <v>0.8308</v>
+      </c>
+      <c r="V8" s="77" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="W8" s="77" t="n">
+        <v>0.8554</v>
+      </c>
+      <c r="X8" s="77" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="Y8" s="77" t="n">
+        <v>0.8702</v>
+      </c>
+      <c r="Z8" s="77" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="AA8" s="77" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AB8" s="77" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="AC8" s="77" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="AD8" s="77" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="AE8" s="77" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="AF8" s="77" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="AG8" s="77" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="AH8" s="77" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="AI8" s="77" t="n">
+        <v>0.6793</v>
+      </c>
+      <c r="AJ8" s="77" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="AK8" s="77" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="AL8" s="77" t="n">
+        <v>0.7121</v>
+      </c>
+      <c r="AM8" s="77" t="n">
+        <v>0.7151</v>
+      </c>
+      <c r="AN8" s="77" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AO8" s="77" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AP8" s="78" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AQ8" s="79" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="77" t="n">
+        <v>0.7816</v>
+      </c>
+      <c r="C9" s="77" t="n">
+        <v>0.7951</v>
+      </c>
+      <c r="D9" s="77" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="E9" s="77" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="F9" s="77" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="G9" s="77" t="n">
+        <v>0.8762</v>
+      </c>
+      <c r="H9" s="77" t="n">
+        <v>0.9032</v>
+      </c>
+      <c r="I9" s="77" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="J9" s="77" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="K9" s="77" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="L9" s="77" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="M9" s="77" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="N9" s="77" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="O9" s="77" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="P9" s="77" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="Q9" s="77" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="R9" s="77" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="S9" s="77" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="T9" s="77" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="U9" s="77" t="n">
+        <v>0.8174</v>
+      </c>
+      <c r="V9" s="77" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="W9" s="77" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="X9" s="77" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="Y9" s="77" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="Z9" s="77" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AA9" s="77" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AB9" s="77" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="AC9" s="77" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="AD9" s="77" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AE9" s="77" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="AF9" s="77" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="AG9" s="77" t="n">
+        <v>0.2292</v>
+      </c>
+      <c r="AH9" s="77" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="AI9" s="77" t="n">
+        <v>0.6655</v>
+      </c>
+      <c r="AJ9" s="77" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="AK9" s="77" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="AL9" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="AM9" s="77" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="AN9" s="77" t="n">
+        <v>0.7262</v>
+      </c>
+      <c r="AO9" s="77" t="n">
+        <v>0.7224</v>
+      </c>
+      <c r="AP9" s="78" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AQ9" s="79" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="77" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="C10" s="77" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="D10" s="77" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="E10" s="77" t="n">
+        <v>0.8293</v>
+      </c>
+      <c r="F10" s="77" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="G10" s="77" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="H10" s="77" t="n">
+        <v>0.9019</v>
+      </c>
+      <c r="I10" s="77" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="J10" s="77" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K10" s="77" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="L10" s="77" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="M10" s="77" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="N10" s="77" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="O10" s="77" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="P10" s="77" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="Q10" s="77" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R10" s="77" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="S10" s="77" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="T10" s="77" t="n">
+        <v>0.7753</v>
+      </c>
+      <c r="U10" s="77" t="n">
+        <v>0.8052</v>
+      </c>
+      <c r="V10" s="77" t="n">
+        <v>0.8351</v>
+      </c>
+      <c r="W10" s="77" t="n">
+        <v>0.8426</v>
+      </c>
+      <c r="X10" s="77" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="Y10" s="77" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="Z10" s="77" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AA10" s="77" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AB10" s="77" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AC10" s="77" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AD10" s="77" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="AE10" s="77" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="AF10" s="77" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="AG10" s="77" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AH10" s="77" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="AI10" s="77" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="AJ10" s="77" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AK10" s="77" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="AL10" s="77" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="AM10" s="77" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="AN10" s="77" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="AO10" s="77" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="AP10" s="78" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AQ10" s="79" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="76" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="77" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="C11" s="77" t="n">
+        <v>0.7528</v>
+      </c>
+      <c r="D11" s="77" t="n">
+        <v>0.7805</v>
+      </c>
+      <c r="E11" s="77" t="n">
+        <v>0.8175</v>
+      </c>
+      <c r="F11" s="77" t="n">
+        <v>0.8545</v>
+      </c>
+      <c r="G11" s="77" t="n">
+        <v>0.8638</v>
+      </c>
+      <c r="H11" s="77" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="I11" s="77" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="J11" s="77" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="K11" s="77" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="L11" s="77" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M11" s="77" t="n">
+        <v>0.2057</v>
+      </c>
+      <c r="N11" s="77" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="O11" s="77" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="P11" s="77" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="Q11" s="77" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="R11" s="77" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="S11" s="77" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="T11" s="77" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U11" s="77" t="n">
+        <v>0.7943</v>
+      </c>
+      <c r="V11" s="77" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="W11" s="77" t="n">
+        <v>0.8371</v>
+      </c>
+      <c r="X11" s="77" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="Y11" s="77" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="Z11" s="77" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA11" s="77" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AB11" s="77" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AC11" s="77" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AD11" s="77" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AE11" s="77" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AF11" s="77" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="AG11" s="77" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="AH11" s="77" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="AI11" s="77" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="AJ11" s="77" t="n">
+        <v>0.6574</v>
+      </c>
+      <c r="AK11" s="77" t="n">
+        <v>0.6781</v>
+      </c>
+      <c r="AL11" s="77" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="AM11" s="77" t="n">
+        <v>0.7040999999999999</v>
+      </c>
+      <c r="AN11" s="77" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="AO11" s="77" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="AP11" s="78" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AQ11" s="79" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="76" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="77" t="n">
+        <v>0.7139</v>
+      </c>
+      <c r="C12" s="77" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="D12" s="77" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="E12" s="77" t="n">
+        <v>0.8068</v>
+      </c>
+      <c r="F12" s="77" t="n">
+        <v>0.8481</v>
+      </c>
+      <c r="G12" s="77" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="H12" s="77" t="n">
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="I12" s="77" t="n">
+        <v>0.8894</v>
+      </c>
+      <c r="J12" s="77" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="K12" s="77" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="L12" s="77" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="M12" s="77" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="N12" s="77" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="O12" s="77" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="P12" s="77" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="Q12" s="77" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="R12" s="77" t="n">
+        <v>0.6983</v>
+      </c>
+      <c r="S12" s="77" t="n">
+        <v>0.7174</v>
+      </c>
+      <c r="T12" s="77" t="n">
+        <v>0.7461</v>
+      </c>
+      <c r="U12" s="77" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="V12" s="77" t="n">
+        <v>0.8226</v>
+      </c>
+      <c r="W12" s="77" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="X12" s="77" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="Y12" s="77" t="n">
+        <v>0.8609</v>
+      </c>
+      <c r="Z12" s="77" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AA12" s="77" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AB12" s="77" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AC12" s="77" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AD12" s="77" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="AE12" s="77" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="AF12" s="77" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AG12" s="77" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="AH12" s="77" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AI12" s="77" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="AJ12" s="77" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AK12" s="77" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="AL12" s="77" t="n">
+        <v>0.6953</v>
+      </c>
+      <c r="AM12" s="77" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+      <c r="AN12" s="77" t="n">
+        <v>0.7242</v>
+      </c>
+      <c r="AO12" s="77" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="AP12" s="78" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AQ12" s="79" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="76" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="77" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="C13" s="77" t="n">
+        <v>0.7181</v>
+      </c>
+      <c r="D13" s="77" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="E13" s="77" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="F13" s="77" t="n">
+        <v>0.8423</v>
+      </c>
+      <c r="G13" s="77" t="n">
+        <v>0.8536</v>
+      </c>
+      <c r="H13" s="77" t="n">
+        <v>0.8987000000000001</v>
+      </c>
+      <c r="I13" s="77" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="J13" s="77" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="K13" s="77" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="L13" s="77" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="M13" s="77" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="N13" s="77" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="O13" s="77" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="P13" s="77" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="Q13" s="77" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="R13" s="77" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="S13" s="77" t="n">
+        <v>0.7020999999999999</v>
+      </c>
+      <c r="T13" s="77" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="U13" s="77" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="V13" s="77" t="n">
+        <v>0.8172</v>
+      </c>
+      <c r="W13" s="77" t="n">
+        <v>0.8277</v>
+      </c>
+      <c r="X13" s="77" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="Y13" s="77" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="Z13" s="77" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AA13" s="77" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AB13" s="77" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AC13" s="77" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AD13" s="77" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="AE13" s="77" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AF13" s="77" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="AG13" s="77" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="AH13" s="77" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="AI13" s="77" t="n">
+        <v>0.6223</v>
+      </c>
+      <c r="AJ13" s="77" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="AK13" s="77" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AL13" s="77" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AM13" s="77" t="n">
+        <v>0.6983</v>
+      </c>
+      <c r="AN13" s="77" t="n">
+        <v>0.7237</v>
+      </c>
+      <c r="AO13" s="77" t="n">
+        <v>0.7173</v>
+      </c>
+      <c r="AP13" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ13" s="79" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="76" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="77" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="C14" s="77" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="D14" s="77" t="n">
+        <v>0.7397</v>
+      </c>
+      <c r="E14" s="77" t="n">
+        <v>0.7883</v>
+      </c>
+      <c r="F14" s="77" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="G14" s="77" t="n">
+        <v>0.8492</v>
+      </c>
+      <c r="H14" s="77" t="n">
+        <v>0.8978</v>
+      </c>
+      <c r="I14" s="77" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="J14" s="77" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="K14" s="77" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="L14" s="77" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="M14" s="77" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="N14" s="77" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="O14" s="77" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="P14" s="77" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="Q14" s="77" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="R14" s="77" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="S14" s="77" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="T14" s="77" t="n">
+        <v>0.7221</v>
+      </c>
+      <c r="U14" s="77" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="V14" s="77" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="W14" s="77" t="n">
+        <v>0.8236</v>
+      </c>
+      <c r="X14" s="77" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="Y14" s="77" t="n">
+        <v>0.8574000000000001</v>
+      </c>
+      <c r="Z14" s="77" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="AA14" s="77" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AB14" s="77" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AC14" s="77" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AD14" s="77" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="AE14" s="77" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="AF14" s="77" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="AG14" s="77" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="AH14" s="77" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="AI14" s="77" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="AJ14" s="77" t="n">
+        <v>0.6345</v>
+      </c>
+      <c r="AK14" s="77" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="AL14" s="77" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="AM14" s="77" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="AN14" s="77" t="n">
+        <v>0.7232</v>
+      </c>
+      <c r="AO14" s="77" t="n">
+        <v>0.7164</v>
+      </c>
+      <c r="AP14" s="78" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AQ14" s="79" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="77" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="C15" s="77" t="n">
+        <v>0.6897</v>
+      </c>
+      <c r="D15" s="77" t="n">
+        <v>0.7286</v>
+      </c>
+      <c r="E15" s="77" t="n">
+        <v>0.7804</v>
+      </c>
+      <c r="F15" s="77" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="G15" s="77" t="n">
+        <v>0.8452</v>
+      </c>
+      <c r="H15" s="77" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="I15" s="77" t="n">
+        <v>0.8841</v>
+      </c>
+      <c r="J15" s="77" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="K15" s="77" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="L15" s="77" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="M15" s="77" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="N15" s="77" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="O15" s="77" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="P15" s="77" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="Q15" s="77" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="R15" s="77" t="n">
+        <v>0.6518</v>
+      </c>
+      <c r="S15" s="77" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="T15" s="77" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="U15" s="77" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="V15" s="77" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="W15" s="77" t="n">
+        <v>0.8199</v>
+      </c>
+      <c r="X15" s="77" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="Y15" s="77" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="Z15" s="77" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="AA15" s="77" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AB15" s="77" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AC15" s="77" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AD15" s="77" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AE15" s="77" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="AF15" s="77" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="AG15" s="77" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="AH15" s="80" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="AI15" s="77" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="AJ15" s="77" t="n">
+        <v>0.6282</v>
+      </c>
+      <c r="AK15" s="77" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="AL15" s="77" t="n">
+        <v>0.6864</v>
+      </c>
+      <c r="AM15" s="77" t="n">
+        <v>0.6937</v>
+      </c>
+      <c r="AN15" s="77" t="n">
+        <v>0.7227</v>
+      </c>
+      <c r="AO15" s="77" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="AP15" s="78" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AQ15" s="79" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="76" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="77" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="C16" s="77" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="D16" s="77" t="n">
+        <v>0.7185</v>
+      </c>
+      <c r="E16" s="77" t="n">
+        <v>0.7732</v>
+      </c>
+      <c r="F16" s="77" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="G16" s="77" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="H16" s="77" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="I16" s="77" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="J16" s="77" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="K16" s="77" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="L16" s="77" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="M16" s="77" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="N16" s="77" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="O16" s="77" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="P16" s="77" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="Q16" s="77" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="R16" s="77" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="S16" s="77" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="T16" s="77" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="U16" s="77" t="n">
+        <v>0.7532</v>
+      </c>
+      <c r="V16" s="77" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="W16" s="77" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="X16" s="77" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="Y16" s="77" t="n">
+        <v>0.8546</v>
+      </c>
+      <c r="Z16" s="77" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="AA16" s="77" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="AB16" s="77" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AC16" s="77" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AD16" s="77" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AE16" s="77" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AF16" s="77" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="AG16" s="77" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="AH16" s="80" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="AI16" s="80" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="AJ16" s="77" t="n">
+        <v>0.6226</v>
+      </c>
+      <c r="AK16" s="77" t="n">
+        <v>0.6533</v>
+      </c>
+      <c r="AL16" s="77" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AM16" s="77" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="AN16" s="77" t="n">
+        <v>0.7223000000000001</v>
+      </c>
+      <c r="AO16" s="77" t="n">
+        <v>0.7147</v>
+      </c>
+      <c r="AP16" s="78" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AQ16" s="79" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="77" t="n">
+        <v>0.6378</v>
+      </c>
+      <c r="C17" s="77" t="n">
+        <v>0.6665</v>
+      </c>
+      <c r="D17" s="77" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="E17" s="77" t="n">
+        <v>0.7667</v>
+      </c>
+      <c r="F17" s="77" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="G17" s="77" t="n">
+        <v>0.8384</v>
+      </c>
+      <c r="H17" s="77" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="I17" s="77" t="n">
+        <v>0.8813</v>
+      </c>
+      <c r="J17" s="77" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="K17" s="77" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="L17" s="77" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="M17" s="77" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="N17" s="77" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="O17" s="77" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="P17" s="77" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="Q17" s="77" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="R17" s="77" t="n">
+        <v>0.6277</v>
+      </c>
+      <c r="S17" s="77" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="T17" s="77" t="n">
+        <v>0.6941000000000001</v>
+      </c>
+      <c r="U17" s="77" t="n">
+        <v>0.7472</v>
+      </c>
+      <c r="V17" s="77" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="W17" s="77" t="n">
+        <v>0.8136</v>
+      </c>
+      <c r="X17" s="77" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="Y17" s="77" t="n">
+        <v>0.8534</v>
+      </c>
+      <c r="Z17" s="80" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AA17" s="77" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AB17" s="77" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AC17" s="77" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AD17" s="77" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="AE17" s="77" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AF17" s="77" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="AG17" s="77" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="AH17" s="80" t="n">
+        <v>0.5773</v>
+      </c>
+      <c r="AI17" s="80" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="AJ17" s="77" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="AK17" s="77" t="n">
+        <v>0.6496</v>
+      </c>
+      <c r="AL17" s="77" t="n">
+        <v>0.6818</v>
+      </c>
+      <c r="AM17" s="77" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="AN17" s="77" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AO17" s="77" t="n">
+        <v>0.7139</v>
+      </c>
+      <c r="AP17" s="78" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AQ17" s="79" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="77" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="C18" s="77" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="D18" s="77" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="E18" s="77" t="n">
+        <v>0.7609</v>
+      </c>
+      <c r="F18" s="77" t="n">
+        <v>0.8205</v>
+      </c>
+      <c r="G18" s="77" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="H18" s="77" t="n">
+        <v>0.8951</v>
+      </c>
+      <c r="I18" s="77" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="J18" s="77" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="K18" s="77" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="L18" s="77" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="M18" s="77" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="N18" s="77" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="O18" s="77" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="P18" s="77" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="Q18" s="77" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="R18" s="77" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="S18" s="77" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="T18" s="77" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="U18" s="77" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="V18" s="77" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="W18" s="77" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="X18" s="77" t="n">
+        <v>0.8662</v>
+      </c>
+      <c r="Y18" s="77" t="n">
+        <v>0.8524</v>
+      </c>
+      <c r="Z18" s="80" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="AA18" s="77" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AB18" s="77" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AC18" s="77" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AD18" s="77" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AE18" s="77" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AF18" s="77" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="AG18" s="77" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="AH18" s="80" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AI18" s="80" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="AJ18" s="77" t="n">
+        <v>0.6129</v>
+      </c>
+      <c r="AK18" s="77" t="n">
+        <v>0.6463</v>
+      </c>
+      <c r="AL18" s="77" t="n">
+        <v>0.6798</v>
+      </c>
+      <c r="AM18" s="77" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="AN18" s="77" t="n">
+        <v>0.7216</v>
+      </c>
+      <c r="AO18" s="77" t="n">
+        <v>0.7133</v>
+      </c>
+      <c r="AP18" s="78" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AQ18" s="79" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="76" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="77" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="C19" s="77" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="D19" s="77" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="E19" s="77" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="F19" s="77" t="n">
+        <v>0.8173</v>
+      </c>
+      <c r="G19" s="77" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="H19" s="77" t="n">
+        <v>0.8946</v>
+      </c>
+      <c r="I19" s="77" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="J19" s="77" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="K19" s="77" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="L19" s="77" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="M19" s="77" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="N19" s="77" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="O19" s="77" t="n">
+        <v>0.1916</v>
+      </c>
+      <c r="P19" s="77" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="Q19" s="77" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="R19" s="77" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="S19" s="77" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="T19" s="77" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="U19" s="77" t="n">
+        <v>0.7369</v>
+      </c>
+      <c r="V19" s="77" t="n">
+        <v>0.7941</v>
+      </c>
+      <c r="W19" s="77" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="X19" s="77" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="Y19" s="77" t="n">
+        <v>0.8514</v>
+      </c>
+      <c r="Z19" s="80" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="AA19" s="77" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AB19" s="77" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AC19" s="77" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AD19" s="77" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="AE19" s="77" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AF19" s="77" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="AG19" s="77" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="AH19" s="80" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="AI19" s="80" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="AJ19" s="77" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="AK19" s="77" t="n">
+        <v>0.6434</v>
+      </c>
+      <c r="AL19" s="77" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="AM19" s="77" t="n">
+        <v>0.6867</v>
+      </c>
+      <c r="AN19" s="77" t="n">
+        <v>0.7213000000000001</v>
+      </c>
+      <c r="AO19" s="77" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="AP19" s="78" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AQ19" s="79" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="76" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="77" t="n">
+        <v>0.6074000000000001</v>
+      </c>
+      <c r="C20" s="77" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="D20" s="77" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="E20" s="77" t="n">
+        <v>0.7507</v>
+      </c>
+      <c r="F20" s="77" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="G20" s="77" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="H20" s="77" t="n">
+        <v>0.8941</v>
+      </c>
+      <c r="I20" s="77" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="J20" s="80" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="K20" s="77" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="L20" s="77" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="M20" s="77" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="N20" s="77" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="O20" s="77" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="P20" s="77" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="Q20" s="77" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="R20" s="80" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="S20" s="77" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="T20" s="77" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="U20" s="77" t="n">
+        <v>0.7324000000000001</v>
+      </c>
+      <c r="V20" s="77" t="n">
+        <v>0.7914</v>
+      </c>
+      <c r="W20" s="77" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="X20" s="77" t="n">
+        <v>0.8652</v>
+      </c>
+      <c r="Y20" s="77" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="Z20" s="80" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="AA20" s="80" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="AB20" s="77" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AC20" s="77" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AD20" s="77" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AE20" s="77" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AF20" s="77" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="AG20" s="77" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="AH20" s="80" t="n">
+        <v>0.5603</v>
+      </c>
+      <c r="AI20" s="80" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="AJ20" s="77" t="n">
+        <v>0.6049</v>
+      </c>
+      <c r="AK20" s="77" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="AL20" s="77" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="AM20" s="77" t="n">
+        <v>0.6853</v>
+      </c>
+      <c r="AN20" s="77" t="n">
+        <v>0.7211</v>
+      </c>
+      <c r="AO20" s="77" t="n">
+        <v>0.7121</v>
+      </c>
+      <c r="AP20" s="78" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="AQ20" s="79" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="76" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="80" t="n">
+        <v>0.5991</v>
+      </c>
+      <c r="C21" s="77" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="E21" s="77" t="n">
+        <v>0.7464</v>
+      </c>
+      <c r="F21" s="77" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="G21" s="77" t="n">
+        <v>0.8282</v>
+      </c>
+      <c r="H21" s="77" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+      <c r="I21" s="77" t="n">
+        <v>0.8773</v>
+      </c>
+      <c r="J21" s="80" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="K21" s="77" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="L21" s="77" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="M21" s="77" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="N21" s="77" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="O21" s="77" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="P21" s="77" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="Q21" s="77" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="R21" s="80" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="S21" s="77" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="T21" s="77" t="n">
+        <v>0.6677</v>
+      </c>
+      <c r="U21" s="77" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="V21" s="77" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="W21" s="77" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="X21" s="77" t="n">
+        <v>0.8648</v>
+      </c>
+      <c r="Y21" s="77" t="n">
+        <v>0.8497</v>
+      </c>
+      <c r="Z21" s="80" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="AA21" s="80" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="AB21" s="77" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="AC21" s="77" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AD21" s="77" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AE21" s="77" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="AF21" s="77" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="AG21" s="77" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="AH21" s="80" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="AI21" s="80" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="AJ21" s="77" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="AK21" s="77" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="AL21" s="77" t="n">
+        <v>0.6749000000000001</v>
+      </c>
+      <c r="AM21" s="77" t="n">
+        <v>0.6841</v>
+      </c>
+      <c r="AN21" s="77" t="n">
+        <v>0.7208</v>
+      </c>
+      <c r="AO21" s="77" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="AP21" s="78" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AQ21" s="79" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="76" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="80" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="C22" s="77" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="D22" s="77" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="E22" s="77" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="F22" s="77" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="G22" s="77" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="H22" s="77" t="n">
+        <v>0.8932</v>
+      </c>
+      <c r="I22" s="77" t="n">
+        <v>0.8764999999999999</v>
+      </c>
+      <c r="J22" s="80" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="K22" s="77" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="L22" s="77" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="M22" s="77" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="N22" s="77" t="n">
+        <v>0.2132</v>
+      </c>
+      <c r="O22" s="77" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="P22" s="77" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="Q22" s="77" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="R22" s="80" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="S22" s="77" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="T22" s="77" t="n">
+        <v>0.6626</v>
+      </c>
+      <c r="U22" s="77" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="V22" s="77" t="n">
+        <v>0.7868000000000001</v>
+      </c>
+      <c r="W22" s="77" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="X22" s="77" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="Y22" s="77" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="Z22" s="80" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="AA22" s="80" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AB22" s="77" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AC22" s="77" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AD22" s="77" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AE22" s="77" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="AF22" s="77" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="AG22" s="77" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="AH22" s="80" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="AI22" s="80" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="AJ22" s="80" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="AK22" s="77" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AL22" s="77" t="n">
+        <v>0.6736</v>
+      </c>
+      <c r="AM22" s="77" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AN22" s="77" t="n">
+        <v>0.7206</v>
+      </c>
+      <c r="AO22" s="77" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="AP22" s="78" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AQ22" s="79" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="76" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="80" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="C23" s="77" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="D23" s="77" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="E23" s="77" t="n">
+        <v>0.7389</v>
+      </c>
+      <c r="F23" s="77" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="G23" s="77" t="n">
+        <v>0.8244</v>
+      </c>
+      <c r="H23" s="77" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="I23" s="77" t="n">
+        <v>0.8758</v>
+      </c>
+      <c r="J23" s="80" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="K23" s="77" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="L23" s="77" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M23" s="77" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="N23" s="77" t="n">
+        <v>0.2152</v>
+      </c>
+      <c r="O23" s="77" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="P23" s="77" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="Q23" s="77" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="R23" s="80" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="S23" s="77" t="n">
+        <v>0.6104000000000001</v>
+      </c>
+      <c r="T23" s="77" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="U23" s="77" t="n">
+        <v>0.7214</v>
+      </c>
+      <c r="V23" s="77" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="W23" s="77" t="n">
+        <v>0.8007</v>
+      </c>
+      <c r="X23" s="77" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="Y23" s="77" t="n">
+        <v>0.8483000000000001</v>
+      </c>
+      <c r="Z23" s="80" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AA23" s="80" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="AB23" s="77" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AC23" s="77" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AD23" s="77" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AE23" s="77" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AF23" s="77" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="AG23" s="77" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="AH23" s="80" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="AI23" s="80" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="AJ23" s="80" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="AK23" s="77" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="AL23" s="77" t="n">
+        <v>0.6724</v>
+      </c>
+      <c r="AM23" s="77" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="AN23" s="77" t="n">
+        <v>0.7204</v>
+      </c>
+      <c r="AO23" s="77" t="n">
+        <v>0.7108</v>
+      </c>
+      <c r="AP23" s="78" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AQ23" s="79" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="76" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="80" t="n">
+        <v>0.5788</v>
+      </c>
+      <c r="C24" s="77" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="D24" s="77" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="E24" s="77" t="n">
+        <v>0.7357</v>
+      </c>
+      <c r="F24" s="77" t="n">
+        <v>0.8054</v>
+      </c>
+      <c r="G24" s="77" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="H24" s="77" t="n">
+        <v>0.8925999999999999</v>
+      </c>
+      <c r="I24" s="77" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="J24" s="80" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="K24" s="77" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="L24" s="77" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="M24" s="77" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="N24" s="77" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="O24" s="77" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="P24" s="77" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="Q24" s="77" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="R24" s="80" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="S24" s="77" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="T24" s="77" t="n">
+        <v>0.6538</v>
+      </c>
+      <c r="U24" s="77" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="V24" s="77" t="n">
+        <v>0.7831</v>
+      </c>
+      <c r="W24" s="77" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="X24" s="77" t="n">
+        <v>0.8638</v>
+      </c>
+      <c r="Y24" s="77" t="n">
+        <v>0.8477</v>
+      </c>
+      <c r="Z24" s="80" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="AA24" s="80" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="AB24" s="77" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="AC24" s="77" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AD24" s="77" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AE24" s="77" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="AF24" s="77" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="AG24" s="77" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="AH24" s="80" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="AI24" s="80" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="AJ24" s="80" t="n">
+        <v>0.5931</v>
+      </c>
+      <c r="AK24" s="77" t="n">
+        <v>0.6322</v>
+      </c>
+      <c r="AL24" s="77" t="n">
+        <v>0.6713</v>
+      </c>
+      <c r="AM24" s="77" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="AN24" s="77" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="AO24" s="77" t="n">
+        <v>0.7104</v>
+      </c>
+      <c r="AP24" s="78" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AQ24" s="79" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="76" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="80" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="C25" s="77" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="D25" s="77" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="E25" s="77" t="n">
+        <v>0.7327</v>
+      </c>
+      <c r="F25" s="77" t="n">
+        <v>0.8036</v>
+      </c>
+      <c r="G25" s="77" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="H25" s="77" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="I25" s="77" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="J25" s="80" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="K25" s="77" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="L25" s="77" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M25" s="77" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="N25" s="77" t="n">
+        <v>0.2186</v>
+      </c>
+      <c r="O25" s="77" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="P25" s="77" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="Q25" s="77" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="R25" s="80" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="S25" s="77" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="T25" s="77" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="U25" s="77" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="V25" s="77" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="W25" s="77" t="n">
+        <v>0.7979000000000001</v>
+      </c>
+      <c r="X25" s="77" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="Y25" s="77" t="n">
+        <v>0.8471</v>
+      </c>
+      <c r="Z25" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AA25" s="80" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AB25" s="77" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AC25" s="77" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AD25" s="77" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AE25" s="77" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AF25" s="77" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="AG25" s="77" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="AH25" s="80" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="AI25" s="80" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AJ25" s="80" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="AK25" s="77" t="n">
+        <v>0.6306</v>
+      </c>
+      <c r="AL25" s="77" t="n">
+        <v>0.6703</v>
+      </c>
+      <c r="AM25" s="77" t="n">
+        <v>0.6803</v>
+      </c>
+      <c r="AN25" s="77" t="n">
+        <v>0.7201</v>
+      </c>
+      <c r="AO25" s="77" t="n">
+        <v>0.7101</v>
+      </c>
+      <c r="AP25" s="78" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AQ25" s="79" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="76" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="80" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="C26" s="77" t="n">
+        <v>0.6042</v>
+      </c>
+      <c r="D26" s="77" t="n">
+        <v>0.6581</v>
+      </c>
+      <c r="E26" s="77" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="F26" s="77" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="G26" s="77" t="n">
+        <v>0.8201000000000001</v>
+      </c>
+      <c r="H26" s="77" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="I26" s="77" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J26" s="80" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="K26" s="80" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="L26" s="77" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="M26" s="77" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="N26" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O26" s="77" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="P26" s="77" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="Q26" s="77" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="R26" s="80" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="S26" s="80" t="n">
+        <v>0.5966</v>
+      </c>
+      <c r="T26" s="77" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="U26" s="77" t="n">
+        <v>0.7133</v>
+      </c>
+      <c r="V26" s="77" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="W26" s="77" t="n">
+        <v>0.7966</v>
+      </c>
+      <c r="X26" s="77" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="Y26" s="77" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="Z26" s="80" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="AA26" s="80" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AB26" s="77" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AC26" s="77" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AD26" s="77" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="AE26" s="77" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="AF26" s="77" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="AG26" s="77" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="AH26" s="80" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="AI26" s="80" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="AJ26" s="80" t="n">
+        <v>0.5887</v>
+      </c>
+      <c r="AK26" s="77" t="n">
+        <v>0.6291</v>
+      </c>
+      <c r="AL26" s="77" t="n">
+        <v>0.6694</v>
+      </c>
+      <c r="AM26" s="77" t="n">
+        <v>0.6795</v>
+      </c>
+      <c r="AN26" s="77" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="AO26" s="77" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="AP26" s="78" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AQ26" s="79" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="76" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="80" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="C27" s="77" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="D27" s="77" t="n">
+        <v>0.6548</v>
+      </c>
+      <c r="E27" s="77" t="n">
+        <v>0.7277</v>
+      </c>
+      <c r="F27" s="77" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="G27" s="77" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="H27" s="77" t="n">
+        <v>0.8918</v>
+      </c>
+      <c r="I27" s="77" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="J27" s="80" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="K27" s="80" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="L27" s="77" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="M27" s="77" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="N27" s="77" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="O27" s="77" t="n">
+        <v>0.2045</v>
+      </c>
+      <c r="P27" s="77" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="Q27" s="77" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="R27" s="80" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="S27" s="80" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="T27" s="77" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="U27" s="77" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="V27" s="77" t="n">
+        <v>0.7786</v>
+      </c>
+      <c r="W27" s="77" t="n">
+        <v>0.7955</v>
+      </c>
+      <c r="X27" s="77" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="Y27" s="77" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="Z27" s="80" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="AA27" s="80" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AB27" s="77" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="AC27" s="77" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AD27" s="77" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AE27" s="77" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AF27" s="77" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="AG27" s="77" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="AH27" s="80" t="n">
+        <v>0.5357</v>
+      </c>
+      <c r="AI27" s="80" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="AJ27" s="80" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="AK27" s="77" t="n">
+        <v>0.6277</v>
+      </c>
+      <c r="AL27" s="77" t="n">
+        <v>0.6686</v>
+      </c>
+      <c r="AM27" s="77" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="AN27" s="77" t="n">
+        <v>0.7198</v>
+      </c>
+      <c r="AO27" s="77" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="AP27" s="78" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AQ27" s="79" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="76" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="80" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="C28" s="80" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="D28" s="77" t="n">
+        <v>0.6518</v>
+      </c>
+      <c r="E28" s="77" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="F28" s="77" t="n">
+        <v>0.7993</v>
+      </c>
+      <c r="G28" s="77" t="n">
+        <v>0.8178</v>
+      </c>
+      <c r="H28" s="77" t="n">
+        <v>0.8915999999999999</v>
+      </c>
+      <c r="I28" s="77" t="n">
+        <v>0.8731</v>
+      </c>
+      <c r="J28" s="80" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="K28" s="80" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="L28" s="77" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="M28" s="77" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="N28" s="77" t="n">
+        <v>0.2226</v>
+      </c>
+      <c r="O28" s="77" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="P28" s="77" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="Q28" s="77" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="R28" s="80" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="S28" s="80" t="n">
+        <v>0.5894</v>
+      </c>
+      <c r="T28" s="77" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="U28" s="77" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="V28" s="77" t="n">
+        <v>0.7774</v>
+      </c>
+      <c r="W28" s="77" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="X28" s="77" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="Y28" s="77" t="n">
+        <v>0.8458</v>
+      </c>
+      <c r="Z28" s="80" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="AA28" s="80" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AB28" s="77" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AC28" s="77" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AD28" s="77" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="AE28" s="77" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AF28" s="77" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="AG28" s="77" t="n">
+        <v>0.2452</v>
+      </c>
+      <c r="AH28" s="80" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="AI28" s="80" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="AJ28" s="80" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="AK28" s="77" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="AL28" s="77" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="AM28" s="77" t="n">
+        <v>0.6783</v>
+      </c>
+      <c r="AN28" s="77" t="n">
+        <v>0.7197</v>
+      </c>
+      <c r="AO28" s="77" t="n">
+        <v>0.7093</v>
+      </c>
+      <c r="AP28" s="78" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="AQ28" s="79" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="76" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="80" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="C29" s="80" t="n">
+        <v>0.5931</v>
+      </c>
+      <c r="D29" s="77" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="E29" s="77" t="n">
+        <v>0.7236</v>
+      </c>
+      <c r="F29" s="77" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="G29" s="77" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="H29" s="77" t="n">
+        <v>0.8914</v>
+      </c>
+      <c r="I29" s="77" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="J29" s="80" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="K29" s="80" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="L29" s="77" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="M29" s="77" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="N29" s="77" t="n">
+        <v>0.2237</v>
+      </c>
+      <c r="O29" s="77" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="P29" s="77" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="Q29" s="77" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="R29" s="80" t="n">
+        <v>0.5517</v>
+      </c>
+      <c r="S29" s="80" t="n">
+        <v>0.5863</v>
+      </c>
+      <c r="T29" s="77" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="U29" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="V29" s="77" t="n">
+        <v>0.7763</v>
+      </c>
+      <c r="W29" s="77" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="X29" s="77" t="n">
+        <v>0.8627</v>
+      </c>
+      <c r="Y29" s="77" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="Z29" s="80" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="AA29" s="80" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AB29" s="77" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="AC29" s="77" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AD29" s="77" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AE29" s="77" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="AF29" s="77" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AG29" s="77" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="AH29" s="80" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="AI29" s="80" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="AJ29" s="80" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="AK29" s="77" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="AL29" s="77" t="n">
+        <v>0.6673</v>
+      </c>
+      <c r="AM29" s="77" t="n">
+        <v>0.6777</v>
+      </c>
+      <c r="AN29" s="77" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="AO29" s="77" t="n">
+        <v>0.7091</v>
+      </c>
+      <c r="AP29" s="78" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="AQ29" s="79" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="76" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="80" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="C30" s="80" t="n">
+        <v>0.5901</v>
+      </c>
+      <c r="D30" s="77" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="E30" s="77" t="n">
+        <v>0.7218</v>
+      </c>
+      <c r="F30" s="77" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="G30" s="77" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="H30" s="77" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="I30" s="77" t="n">
+        <v>0.8724</v>
+      </c>
+      <c r="J30" s="80" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="K30" s="80" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="L30" s="77" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="M30" s="77" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="N30" s="77" t="n">
+        <v>0.2246</v>
+      </c>
+      <c r="O30" s="77" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="P30" s="77" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="Q30" s="77" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="R30" s="80" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="S30" s="80" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="T30" s="77" t="n">
+        <v>0.6358</v>
+      </c>
+      <c r="U30" s="77" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="V30" s="77" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="W30" s="77" t="n">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="X30" s="77" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="Y30" s="77" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="Z30" s="80" t="n">
+        <v>0.4642</v>
+      </c>
+      <c r="AA30" s="80" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AB30" s="77" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="AC30" s="77" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AD30" s="77" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AE30" s="77" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AF30" s="77" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="AG30" s="77" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="AH30" s="81" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="AI30" s="80" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="AJ30" s="80" t="n">
+        <v>0.5822000000000001</v>
+      </c>
+      <c r="AK30" s="77" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="AL30" s="77" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AM30" s="77" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="AN30" s="77" t="n">
+        <v>0.7194</v>
+      </c>
+      <c r="AO30" s="77" t="n">
+        <v>0.7089</v>
+      </c>
+      <c r="AP30" s="78" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AQ30" s="79" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="76" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="80" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="C31" s="80" t="n">
+        <v>0.5874</v>
+      </c>
+      <c r="D31" s="77" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="E31" s="77" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="F31" s="77" t="n">
+        <v>0.7961</v>
+      </c>
+      <c r="G31" s="77" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="H31" s="77" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="I31" s="77" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="J31" s="80" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="K31" s="80" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="L31" s="77" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="M31" s="77" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="N31" s="77" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="O31" s="77" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="P31" s="77" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="Q31" s="77" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="R31" s="80" t="n">
+        <v>0.5458</v>
+      </c>
+      <c r="S31" s="80" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="T31" s="77" t="n">
+        <v>0.6338</v>
+      </c>
+      <c r="U31" s="77" t="n">
+        <v>0.7040999999999999</v>
+      </c>
+      <c r="V31" s="77" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="W31" s="77" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="X31" s="77" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="Y31" s="77" t="n">
+        <v>0.8448</v>
+      </c>
+      <c r="Z31" s="80" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="AA31" s="80" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="AB31" s="80" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AC31" s="77" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AD31" s="77" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AE31" s="77" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AF31" s="77" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AG31" s="77" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="AH31" s="81" t="n">
+        <v>0.5276999999999999</v>
+      </c>
+      <c r="AI31" s="80" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AJ31" s="80" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="AK31" s="77" t="n">
+        <v>0.6235000000000001</v>
+      </c>
+      <c r="AL31" s="77" t="n">
+        <v>0.6661</v>
+      </c>
+      <c r="AM31" s="77" t="n">
+        <v>0.6768</v>
+      </c>
+      <c r="AN31" s="77" t="n">
+        <v>0.7194</v>
+      </c>
+      <c r="AO31" s="77" t="n">
+        <v>0.7087</v>
+      </c>
+      <c r="AP31" s="78" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AQ31" s="79" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="76" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="80" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="C32" s="80" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="D32" s="77" t="n">
+        <v>0.6423</v>
+      </c>
+      <c r="E32" s="77" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="F32" s="77" t="n">
+        <v>0.7953</v>
+      </c>
+      <c r="G32" s="77" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="H32" s="77" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="I32" s="77" t="n">
+        <v>0.8718</v>
+      </c>
+      <c r="J32" s="80" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="K32" s="80" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="L32" s="77" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="M32" s="77" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="N32" s="77" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="O32" s="77" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="P32" s="77" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="Q32" s="77" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="R32" s="80" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="S32" s="80" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="T32" s="77" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="U32" s="77" t="n">
+        <v>0.7028</v>
+      </c>
+      <c r="V32" s="77" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="W32" s="77" t="n">
+        <v>0.7914</v>
+      </c>
+      <c r="X32" s="77" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="Y32" s="77" t="n">
+        <v>0.8446</v>
+      </c>
+      <c r="Z32" s="80" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="AA32" s="80" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AB32" s="80" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="AC32" s="77" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AD32" s="77" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AE32" s="77" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AF32" s="77" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="AG32" s="77" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="AH32" s="81" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="AI32" s="80" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="AJ32" s="80" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="AK32" s="77" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="AL32" s="77" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="AM32" s="77" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="AN32" s="77" t="n">
+        <v>0.7193000000000001</v>
+      </c>
+      <c r="AO32" s="77" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="AP32" s="78" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AQ32" s="79" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="76" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="80" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="C33" s="80" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="D33" s="77" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="E33" s="77" t="n">
+        <v>0.7175</v>
+      </c>
+      <c r="F33" s="77" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="G33" s="77" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="H33" s="77" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="I33" s="77" t="n">
+        <v>0.8715000000000001</v>
+      </c>
+      <c r="J33" s="80" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="K33" s="80" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="L33" s="77" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M33" s="77" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="N33" s="77" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="O33" s="77" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="P33" s="77" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="Q33" s="77" t="n">
+        <v>0.1557</v>
+      </c>
+      <c r="R33" s="80" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="S33" s="80" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="T33" s="77" t="n">
+        <v>0.6302</v>
+      </c>
+      <c r="U33" s="77" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="V33" s="77" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="W33" s="77" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="X33" s="77" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="Y33" s="77" t="n">
+        <v>0.8443000000000001</v>
+      </c>
+      <c r="Z33" s="80" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="AA33" s="80" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AB33" s="80" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="AC33" s="77" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AD33" s="77" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AE33" s="77" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AF33" s="77" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="AG33" s="77" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="AH33" s="81" t="n">
+        <v>0.5248</v>
+      </c>
+      <c r="AI33" s="80" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="AJ33" s="80" t="n">
+        <v>0.5788</v>
+      </c>
+      <c r="AK33" s="77" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AL33" s="77" t="n">
+        <v>0.6652</v>
+      </c>
+      <c r="AM33" s="77" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AN33" s="77" t="n">
+        <v>0.7192</v>
+      </c>
+      <c r="AO33" s="77" t="n">
+        <v>0.7084</v>
+      </c>
+      <c r="AP33" s="78" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AQ33" s="79" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="76" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="80" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="C34" s="80" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="D34" s="77" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="E34" s="77" t="n">
+        <v>0.7163</v>
+      </c>
+      <c r="F34" s="77" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="G34" s="77" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="H34" s="77" t="n">
+        <v>0.8905999999999999</v>
+      </c>
+      <c r="I34" s="77" t="n">
+        <v>0.8713</v>
+      </c>
+      <c r="J34" s="80" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="K34" s="80" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="L34" s="77" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="M34" s="77" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="N34" s="77" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="O34" s="77" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="P34" s="77" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="Q34" s="77" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="R34" s="80" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="S34" s="80" t="n">
+        <v>0.5748</v>
+      </c>
+      <c r="T34" s="77" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="U34" s="77" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="V34" s="77" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="W34" s="77" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="X34" s="77" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Y34" s="77" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="Z34" s="81" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="AA34" s="80" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="AB34" s="80" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="AC34" s="77" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="AD34" s="77" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AE34" s="77" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="AF34" s="77" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="AG34" s="77" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="AH34" s="81" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="AI34" s="80" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="AJ34" s="80" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="AK34" s="77" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="AL34" s="77" t="n">
+        <v>0.6647999999999999</v>
+      </c>
+      <c r="AM34" s="77" t="n">
+        <v>0.6757</v>
+      </c>
+      <c r="AN34" s="77" t="n">
+        <v>0.7191</v>
+      </c>
+      <c r="AO34" s="77" t="n">
+        <v>0.7083</v>
+      </c>
+      <c r="AP34" s="78" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AQ34" s="79" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="76" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="80" t="n">
+        <v>0.5399</v>
+      </c>
+      <c r="C35" s="80" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="D35" s="77" t="n">
+        <v>0.6373</v>
+      </c>
+      <c r="E35" s="77" t="n">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="F35" s="77" t="n">
+        <v>0.7931</v>
+      </c>
+      <c r="G35" s="77" t="n">
+        <v>0.8126</v>
+      </c>
+      <c r="H35" s="77" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="I35" s="77" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="J35" s="80" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="K35" s="80" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="L35" s="77" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="M35" s="77" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="N35" s="77" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="O35" s="77" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="P35" s="77" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="Q35" s="77" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="R35" s="80" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="S35" s="80" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="T35" s="77" t="n">
+        <v>0.6272</v>
+      </c>
+      <c r="U35" s="77" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="V35" s="77" t="n">
+        <v>0.7717000000000001</v>
+      </c>
+      <c r="W35" s="77" t="n">
+        <v>0.7897</v>
+      </c>
+      <c r="X35" s="77" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="Y35" s="77" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="Z35" s="81" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="AA35" s="80" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="AB35" s="80" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AC35" s="77" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AD35" s="77" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AE35" s="77" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AF35" s="77" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="AG35" s="77" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="AH35" s="81" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="AI35" s="80" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="AJ35" s="80" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AK35" s="77" t="n">
+        <v>0.6207</v>
+      </c>
+      <c r="AL35" s="77" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="AM35" s="77" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="AN35" s="77" t="n">
+        <v>0.7191</v>
+      </c>
+      <c r="AO35" s="77" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="AP35" s="78" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AQ35" s="79" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="76" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="80" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="C36" s="80" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="D36" s="77" t="n">
+        <v>0.6359</v>
+      </c>
+      <c r="E36" s="77" t="n">
+        <v>0.7141999999999999</v>
+      </c>
+      <c r="F36" s="77" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="G36" s="77" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="H36" s="77" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="I36" s="77" t="n">
+        <v>0.8708</v>
+      </c>
+      <c r="J36" s="80" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="K36" s="80" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="L36" s="77" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="M36" s="77" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="N36" s="77" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="O36" s="77" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="P36" s="77" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="Q36" s="77" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="R36" s="80" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="S36" s="80" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="T36" s="77" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="U36" s="77" t="n">
+        <v>0.6986</v>
+      </c>
+      <c r="V36" s="77" t="n">
+        <v>0.7711</v>
+      </c>
+      <c r="W36" s="77" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="X36" s="77" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="Y36" s="77" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="Z36" s="81" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AA36" s="80" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="AB36" s="80" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="AC36" s="77" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AD36" s="77" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AE36" s="77" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="AF36" s="77" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="AG36" s="77" t="n">
+        <v>0.2467</v>
+      </c>
+      <c r="AH36" s="81" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="AI36" s="80" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="AJ36" s="80" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="AK36" s="77" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="AL36" s="77" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="AM36" s="77" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="AN36" s="77" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AO36" s="77" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="AP36" s="78" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AQ36" s="79" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="76" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="80" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="C37" s="80" t="n">
+        <v>0.5757</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>0.6347</v>
+      </c>
+      <c r="E37" s="77" t="n">
+        <v>0.7134</v>
+      </c>
+      <c r="F37" s="77" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="G37" s="77" t="n">
+        <v>0.8117</v>
+      </c>
+      <c r="H37" s="77" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="I37" s="77" t="n">
+        <v>0.8707</v>
+      </c>
+      <c r="J37" s="80" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="K37" s="80" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="L37" s="77" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="M37" s="77" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="N37" s="77" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="O37" s="77" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="P37" s="77" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="Q37" s="77" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="R37" s="80" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="S37" s="80" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="T37" s="77" t="n">
+        <v>0.6248</v>
+      </c>
+      <c r="U37" s="77" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="V37" s="77" t="n">
+        <v>0.7706</v>
+      </c>
+      <c r="W37" s="77" t="n">
+        <v>0.7889</v>
+      </c>
+      <c r="X37" s="77" t="n">
+        <v>0.8618</v>
+      </c>
+      <c r="Y37" s="77" t="n">
+        <v>0.8435</v>
+      </c>
+      <c r="Z37" s="81" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="AA37" s="80" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="AB37" s="80" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AC37" s="77" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AD37" s="77" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AE37" s="77" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AF37" s="77" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="AG37" s="77" t="n">
+        <v>0.2469</v>
+      </c>
+      <c r="AH37" s="81" t="n">
+        <v>0.5204</v>
+      </c>
+      <c r="AI37" s="80" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="AJ37" s="80" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="AK37" s="77" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="AL37" s="77" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="AM37" s="77" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="AN37" s="77" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AO37" s="77" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="AP37" s="78" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AQ37" s="79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="76" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="80" t="n">
+        <v>0.5349</v>
+      </c>
+      <c r="C38" s="80" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="D38" s="77" t="n">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="E38" s="77" t="n">
+        <v>0.7126</v>
+      </c>
+      <c r="F38" s="77" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="G38" s="77" t="n">
+        <v>0.8113</v>
+      </c>
+      <c r="H38" s="77" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="I38" s="77" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="J38" s="80" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="K38" s="80" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="L38" s="77" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="M38" s="77" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="N38" s="77" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="O38" s="77" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="P38" s="77" t="n">
+        <v>0.1383</v>
+      </c>
+      <c r="Q38" s="77" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="R38" s="80" t="n">
+        <v>0.5323</v>
+      </c>
+      <c r="S38" s="80" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="T38" s="77" t="n">
+        <v>0.6238</v>
+      </c>
+      <c r="U38" s="77" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="V38" s="77" t="n">
+        <v>0.7702</v>
+      </c>
+      <c r="W38" s="77" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="X38" s="77" t="n">
+        <v>0.8617</v>
+      </c>
+      <c r="Y38" s="77" t="n">
+        <v>0.8434</v>
+      </c>
+      <c r="Z38" s="81" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="AA38" s="80" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="AB38" s="80" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="AC38" s="77" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AD38" s="77" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AE38" s="77" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AF38" s="77" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="AG38" s="77" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="AH38" s="81" t="n">
+        <v>0.5196</v>
+      </c>
+      <c r="AI38" s="80" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="AJ38" s="80" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="AK38" s="77" t="n">
+        <v>0.6192</v>
+      </c>
+      <c r="AL38" s="77" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="AM38" s="77" t="n">
+        <v>0.6746</v>
+      </c>
+      <c r="AN38" s="77" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="AO38" s="77" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="AP38" s="78" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AQ38" s="79" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="76" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="80" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="C39" s="80" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="D39" s="77" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="E39" s="77" t="n">
+        <v>0.7118</v>
+      </c>
+      <c r="F39" s="77" t="n">
+        <v>0.7911</v>
+      </c>
+      <c r="G39" s="77" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="H39" s="77" t="n">
+        <v>0.8902</v>
+      </c>
+      <c r="I39" s="77" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="J39" s="80" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="K39" s="80" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="L39" s="77" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="M39" s="77" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="N39" s="77" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="O39" s="77" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="P39" s="77" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="Q39" s="77" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="R39" s="80" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="S39" s="80" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="T39" s="77" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="U39" s="77" t="n">
+        <v>0.6963</v>
+      </c>
+      <c r="V39" s="77" t="n">
+        <v>0.7698</v>
+      </c>
+      <c r="W39" s="77" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="X39" s="77" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="Y39" s="77" t="n">
+        <v>0.8433</v>
+      </c>
+      <c r="Z39" s="81" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="AA39" s="80" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="AB39" s="80" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="AC39" s="77" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AD39" s="77" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AE39" s="77" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="AF39" s="77" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="AG39" s="77" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="AH39" s="81" t="n">
+        <v>0.5188</v>
+      </c>
+      <c r="AI39" s="80" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="AJ39" s="80" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="AK39" s="77" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="AL39" s="77" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="AM39" s="77" t="n">
+        <v>0.6744</v>
+      </c>
+      <c r="AN39" s="77" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="AO39" s="77" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="AP39" s="78" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AQ39" s="79" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="80" t="n">
+        <v>0.5323</v>
+      </c>
+      <c r="C40" s="80" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="D40" s="77" t="n">
+        <v>0.6317</v>
+      </c>
+      <c r="E40" s="77" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="F40" s="77" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="G40" s="77" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="H40" s="77" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="I40" s="77" t="n">
+        <v>0.8702</v>
+      </c>
+      <c r="J40" s="81" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="K40" s="80" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="L40" s="77" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="M40" s="77" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="N40" s="77" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="O40" s="77" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="P40" s="77" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="Q40" s="77" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="R40" s="81" t="n">
+        <v>0.5299</v>
+      </c>
+      <c r="S40" s="80" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="T40" s="77" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="U40" s="77" t="n">
+        <v>0.6957</v>
+      </c>
+      <c r="V40" s="77" t="n">
+        <v>0.7694</v>
+      </c>
+      <c r="W40" s="77" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="X40" s="77" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="Y40" s="77" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="Z40" s="81" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="AA40" s="80" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AB40" s="80" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="AC40" s="77" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AD40" s="77" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="AE40" s="77" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AF40" s="77" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AG40" s="77" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="AH40" s="81" t="n">
+        <v>0.5181</v>
+      </c>
+      <c r="AI40" s="80" t="n">
+        <v>0.5404</v>
+      </c>
+      <c r="AJ40" s="80" t="n">
+        <v>0.5739</v>
+      </c>
+      <c r="AK40" s="77" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="AL40" s="77" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="AM40" s="77" t="n">
+        <v>0.6742</v>
+      </c>
+      <c r="AN40" s="77" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="AO40" s="77" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="AP40" s="78" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AQ40" s="79" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="76" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="80" t="n">
+        <v>0.5311</v>
+      </c>
+      <c r="C41" s="80" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="D41" s="77" t="n">
+        <v>0.6308</v>
+      </c>
+      <c r="E41" s="77" t="n">
+        <v>0.7106</v>
+      </c>
+      <c r="F41" s="77" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="G41" s="77" t="n">
+        <v>0.8103</v>
+      </c>
+      <c r="H41" s="77" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="I41" s="77" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="J41" s="81" t="n">
+        <v>0.4711</v>
+      </c>
+      <c r="K41" s="80" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="L41" s="77" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="M41" s="77" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="N41" s="77" t="n">
+        <v>0.2309</v>
+      </c>
+      <c r="O41" s="77" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="P41" s="77" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="Q41" s="77" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="R41" s="81" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="S41" s="80" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="T41" s="77" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="U41" s="77" t="n">
+        <v>0.6952</v>
+      </c>
+      <c r="V41" s="77" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="W41" s="77" t="n">
+        <v>0.7876</v>
+      </c>
+      <c r="X41" s="77" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="Y41" s="77" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="Z41" s="81" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="AA41" s="80" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="AB41" s="80" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="AC41" s="77" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AD41" s="77" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AE41" s="77" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AF41" s="77" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AG41" s="77" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="AH41" s="81" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="AI41" s="80" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="AJ41" s="80" t="n">
+        <v>0.5734</v>
+      </c>
+      <c r="AK41" s="77" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="AL41" s="77" t="n">
+        <v>0.6629</v>
+      </c>
+      <c r="AM41" s="77" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="AN41" s="77" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="AO41" s="77" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="AP41" s="78" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="AQ41" s="79" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="76" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="80" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="C42" s="80" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="D42" s="77" t="n">
+        <v>0.6301</v>
+      </c>
+      <c r="E42" s="77" t="n">
+        <v>0.7101</v>
+      </c>
+      <c r="F42" s="77" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G42" s="77" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H42" s="77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I42" s="77" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J42" s="81" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="K42" s="80" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="L42" s="77" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="M42" s="77" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="N42" s="77" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="O42" s="77" t="n">
+        <v>0.2127</v>
+      </c>
+      <c r="P42" s="77" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="Q42" s="77" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="R42" s="81" t="n">
+        <v>0.5279</v>
+      </c>
+      <c r="S42" s="80" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="T42" s="77" t="n">
+        <v>0.6206</v>
+      </c>
+      <c r="U42" s="77" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="V42" s="77" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="W42" s="77" t="n">
+        <v>0.7873</v>
+      </c>
+      <c r="X42" s="77" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="Y42" s="77" t="n">
+        <v>0.8429</v>
+      </c>
+      <c r="Z42" s="81" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="AA42" s="80" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="AB42" s="80" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="AC42" s="77" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AD42" s="77" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AE42" s="77" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="AF42" s="77" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="AG42" s="77" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="AH42" s="81" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AI42" s="80" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="AJ42" s="80" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AK42" s="77" t="n">
+        <v>0.6178</v>
+      </c>
+      <c r="AL42" s="77" t="n">
+        <v>0.6627</v>
+      </c>
+      <c r="AM42" s="77" t="n">
+        <v>0.6739000000000001</v>
+      </c>
+      <c r="AN42" s="77" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="AO42" s="77" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="AP42" s="78" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AQ42" s="79" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="76" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="81" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="C43" s="80" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="D43" s="77" t="n">
+        <v>0.6294</v>
+      </c>
+      <c r="E43" s="77" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="F43" s="77" t="n">
+        <v>0.7897999999999999</v>
+      </c>
+      <c r="G43" s="77" t="n">
+        <v>0.8098</v>
+      </c>
+      <c r="H43" s="77" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I43" s="77" t="n">
+        <v>0.8699</v>
+      </c>
+      <c r="J43" s="81" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="K43" s="80" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="L43" s="77" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M43" s="77" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="N43" s="77" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="O43" s="77" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="P43" s="77" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="Q43" s="77" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="R43" s="81" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="S43" s="80" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="T43" s="77" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="U43" s="77" t="n">
+        <v>0.6943</v>
+      </c>
+      <c r="V43" s="77" t="n">
+        <v>0.7685999999999999</v>
+      </c>
+      <c r="W43" s="77" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="X43" s="77" t="n">
+        <v>0.8614000000000001</v>
+      </c>
+      <c r="Y43" s="77" t="n">
+        <v>0.8429</v>
+      </c>
+      <c r="Z43" s="81" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AA43" s="80" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="AB43" s="80" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="AC43" s="77" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AD43" s="77" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AE43" s="77" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="AF43" s="77" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="AG43" s="77" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="AH43" s="81" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="AI43" s="80" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="AJ43" s="80" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="AK43" s="77" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="AL43" s="77" t="n">
+        <v>0.6625</v>
+      </c>
+      <c r="AM43" s="77" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="AN43" s="77" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="AO43" s="77" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="AP43" s="78" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AQ43" s="79" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="76" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="81" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="C44" s="80" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="D44" s="77" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="E44" s="77" t="n">
+        <v>0.7091</v>
+      </c>
+      <c r="F44" s="77" t="n">
+        <v>0.7895</v>
+      </c>
+      <c r="G44" s="77" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="H44" s="77" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="I44" s="77" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="J44" s="81" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="K44" s="80" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="L44" s="77" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="M44" s="77" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="N44" s="77" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="O44" s="77" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="P44" s="77" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="Q44" s="77" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="R44" s="81" t="n">
+        <v>0.5263</v>
+      </c>
+      <c r="S44" s="80" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="T44" s="77" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="U44" s="77" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="V44" s="77" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="W44" s="77" t="n">
+        <v>0.7869</v>
+      </c>
+      <c r="X44" s="77" t="n">
+        <v>0.8614000000000001</v>
+      </c>
+      <c r="Y44" s="77" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="Z44" s="81" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="AA44" s="80" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="AB44" s="80" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AC44" s="77" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AD44" s="77" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AE44" s="77" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AF44" s="77" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="AG44" s="77" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="AH44" s="81" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="AI44" s="80" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AJ44" s="80" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="AK44" s="77" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="AL44" s="77" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="AM44" s="77" t="n">
+        <v>0.6737</v>
+      </c>
+      <c r="AN44" s="77" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="AO44" s="77" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="AP44" s="78" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AQ44" s="79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="76" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="81" t="n">
+        <v>0.5276</v>
+      </c>
+      <c r="C45" s="80" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="D45" s="77" t="n">
+        <v>0.6283</v>
+      </c>
+      <c r="E45" s="77" t="n">
+        <v>0.7088</v>
+      </c>
+      <c r="F45" s="77" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="G45" s="77" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="H45" s="77" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="I45" s="77" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="J45" s="81" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="K45" s="80" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="L45" s="77" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="M45" s="77" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="N45" s="77" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="O45" s="77" t="n">
+        <v>0.2133</v>
+      </c>
+      <c r="P45" s="77" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="Q45" s="77" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="R45" s="81" t="n">
+        <v>0.5256</v>
+      </c>
+      <c r="S45" s="80" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="T45" s="77" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="U45" s="77" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="V45" s="77" t="n">
+        <v>0.7681</v>
+      </c>
+      <c r="W45" s="77" t="n">
+        <v>0.7867</v>
+      </c>
+      <c r="X45" s="77" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="Y45" s="77" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="Z45" s="81" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="AA45" s="80" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="AB45" s="80" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="AC45" s="77" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AD45" s="77" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AE45" s="77" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="AF45" s="77" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="AG45" s="77" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="AH45" s="81" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="AI45" s="80" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="AJ45" s="80" t="n">
+        <v>0.5719</v>
+      </c>
+      <c r="AK45" s="77" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="AL45" s="77" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="AM45" s="77" t="n">
+        <v>0.6736</v>
+      </c>
+      <c r="AN45" s="77" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="AO45" s="77" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="AP45" s="78" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AQ45" s="79" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="76" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="81" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="C46" s="80" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="D46" s="77" t="n">
+        <v>0.6278</v>
+      </c>
+      <c r="E46" s="77" t="n">
+        <v>0.7084</v>
+      </c>
+      <c r="F46" s="77" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G46" s="77" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="H46" s="77" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I46" s="77" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="J46" s="81" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K46" s="80" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="L46" s="77" t="n">
+        <v>0.3816</v>
+      </c>
+      <c r="M46" s="77" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="N46" s="77" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="O46" s="77" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="P46" s="77" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="Q46" s="77" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="R46" s="81" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="S46" s="80" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="T46" s="77" t="n">
+        <v>0.6183999999999999</v>
+      </c>
+      <c r="U46" s="77" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="V46" s="77" t="n">
+        <v>0.7679</v>
+      </c>
+      <c r="W46" s="77" t="n">
+        <v>0.7866</v>
+      </c>
+      <c r="X46" s="77" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="Y46" s="77" t="n">
+        <v>0.8426</v>
+      </c>
+      <c r="Z46" s="81" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="AA46" s="80" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="AB46" s="80" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="AC46" s="77" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AD46" s="77" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AE46" s="77" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AF46" s="77" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="AG46" s="77" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="AH46" s="81" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="AI46" s="80" t="n">
+        <v>0.5377</v>
+      </c>
+      <c r="AJ46" s="80" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="AK46" s="77" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="AL46" s="77" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="AM46" s="77" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AN46" s="77" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="AO46" s="77" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="AP46" s="78" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="AQ46" s="79" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="76" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="81" t="n">
+        <v>0.5263</v>
+      </c>
+      <c r="C47" s="80" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="D47" s="77" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="E47" s="77" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="F47" s="77" t="n">
+        <v>0.7887999999999999</v>
+      </c>
+      <c r="G47" s="77" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="H47" s="77" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I47" s="77" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="J47" s="81" t="n">
+        <v>0.4756</v>
+      </c>
+      <c r="K47" s="80" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="L47" s="77" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="M47" s="77" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="N47" s="77" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="O47" s="77" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="P47" s="77" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="Q47" s="77" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="R47" s="81" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="S47" s="80" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="T47" s="77" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="U47" s="77" t="n">
+        <v>0.6928</v>
+      </c>
+      <c r="V47" s="77" t="n">
+        <v>0.7677</v>
+      </c>
+      <c r="W47" s="77" t="n">
+        <v>0.7864</v>
+      </c>
+      <c r="X47" s="77" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="Y47" s="77" t="n">
+        <v>0.8426</v>
+      </c>
+      <c r="Z47" s="81" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="AA47" s="80" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="AB47" s="80" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AC47" s="77" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AD47" s="77" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AE47" s="77" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AF47" s="77" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="AG47" s="77" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AH47" s="81" t="n">
+        <v>0.5148</v>
+      </c>
+      <c r="AI47" s="80" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="AJ47" s="80" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="AK47" s="77" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="AL47" s="77" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="AM47" s="77" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="AN47" s="77" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="AO47" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="AP47" s="78" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="AQ47" s="79" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="76" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="81" t="n">
+        <v>0.5258</v>
+      </c>
+      <c r="C48" s="80" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="D48" s="77" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="E48" s="77" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="F48" s="77" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="G48" s="77" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="H48" s="77" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I48" s="77" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="J48" s="81" t="n">
+        <v>0.4761</v>
+      </c>
+      <c r="K48" s="80" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="L48" s="77" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="M48" s="77" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="N48" s="77" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="O48" s="77" t="n">
+        <v>0.2137</v>
+      </c>
+      <c r="P48" s="77" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="Q48" s="77" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="R48" s="81" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="S48" s="80" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="T48" s="77" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="U48" s="77" t="n">
+        <v>0.6926</v>
+      </c>
+      <c r="V48" s="77" t="n">
+        <v>0.7675</v>
+      </c>
+      <c r="W48" s="77" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="X48" s="77" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="Y48" s="77" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="Z48" s="81" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="AA48" s="80" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="AB48" s="80" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="AC48" s="77" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AD48" s="77" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AE48" s="77" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AF48" s="77" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="AG48" s="77" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AH48" s="81" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="AI48" s="80" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="AJ48" s="80" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="AK48" s="77" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="AL48" s="77" t="n">
+        <v>0.6619</v>
+      </c>
+      <c r="AM48" s="77" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="AN48" s="77" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="AO48" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="AP48" s="78" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="AQ48" s="79" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="76" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="81" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="C49" s="80" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="D49" s="77" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E49" s="77" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="F49" s="77" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="G49" s="77" t="n">
+        <v>0.8088</v>
+      </c>
+      <c r="H49" s="77" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="I49" s="77" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="J49" s="81" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="K49" s="80" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L49" s="77" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="M49" s="77" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="N49" s="77" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="O49" s="77" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="P49" s="77" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="Q49" s="77" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="R49" s="81" t="n">
+        <v>0.5234</v>
+      </c>
+      <c r="S49" s="80" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="T49" s="77" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="U49" s="77" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="V49" s="77" t="n">
+        <v>0.7674</v>
+      </c>
+      <c r="W49" s="77" t="n">
+        <v>0.7862</v>
+      </c>
+      <c r="X49" s="77" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="Y49" s="77" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="Z49" s="81" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="AA49" s="80" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="AB49" s="80" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="AC49" s="77" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AD49" s="77" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AE49" s="77" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AF49" s="77" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="AG49" s="77" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AH49" s="81" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="AI49" s="80" t="n">
+        <v>0.5369</v>
+      </c>
+      <c r="AJ49" s="80" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AK49" s="77" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="AL49" s="77" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="AM49" s="77" t="n">
+        <v>0.6732</v>
+      </c>
+      <c r="AN49" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO49" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="AP49" s="78" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AQ49" s="79" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="76" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="81" t="n">
+        <v>0.5248</v>
+      </c>
+      <c r="C50" s="80" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="D50" s="77" t="n">
+        <v>0.6262</v>
+      </c>
+      <c r="E50" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="F50" s="77" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="G50" s="77" t="n">
+        <v>0.8086</v>
+      </c>
+      <c r="H50" s="77" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I50" s="77" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="J50" s="81" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="K50" s="80" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="L50" s="77" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="M50" s="77" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="N50" s="77" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="O50" s="77" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="P50" s="77" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="Q50" s="77" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="R50" s="81" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="S50" s="80" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="T50" s="77" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="U50" s="77" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="V50" s="77" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="W50" s="77" t="n">
+        <v>0.7861</v>
+      </c>
+      <c r="X50" s="77" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="Y50" s="77" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="Z50" s="81" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="AA50" s="80" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="AB50" s="80" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="AC50" s="77" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="AD50" s="77" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AE50" s="77" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AF50" s="77" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="AG50" s="77" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AH50" s="81" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="AI50" s="80" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="AJ50" s="80" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="AK50" s="77" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="AL50" s="77" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="AM50" s="77" t="n">
+        <v>0.6731</v>
+      </c>
+      <c r="AN50" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO50" s="77" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="AP50" s="78" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="AQ50" s="79" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="76" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="81" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="C51" s="80" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="D51" s="77" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="E51" s="77" t="n">
+        <v>0.7071</v>
+      </c>
+      <c r="F51" s="77" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="G51" s="77" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="H51" s="77" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I51" s="77" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="J51" s="81" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="K51" s="80" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="L51" s="77" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="M51" s="77" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="N51" s="77" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="O51" s="77" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="P51" s="77" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="Q51" s="77" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="R51" s="81" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="S51" s="80" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="T51" s="77" t="n">
+        <v>0.6167</v>
+      </c>
+      <c r="U51" s="77" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="V51" s="77" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="W51" s="77" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="X51" s="77" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="Y51" s="77" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="Z51" s="81" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="AA51" s="80" t="n">
+        <v>0.4556</v>
+      </c>
+      <c r="AB51" s="80" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AC51" s="77" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AD51" s="77" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AE51" s="77" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AF51" s="77" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AG51" s="77" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AH51" s="81" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="AI51" s="80" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="AJ51" s="80" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="AK51" s="77" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="AL51" s="77" t="n">
+        <v>0.6617</v>
+      </c>
+      <c r="AM51" s="77" t="n">
+        <v>0.6731</v>
+      </c>
+      <c r="AN51" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO51" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="AP51" s="78" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="AQ51" s="79" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="76" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="81" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="C52" s="80" t="n">
+        <v>0.5647</v>
+      </c>
+      <c r="D52" s="77" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="E52" s="77" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="F52" s="77" t="n">
+        <v>0.7881</v>
+      </c>
+      <c r="G52" s="77" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="H52" s="77" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I52" s="77" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="J52" s="81" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="K52" s="80" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="L52" s="77" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="M52" s="77" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="N52" s="77" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="O52" s="77" t="n">
+        <v>0.2141</v>
+      </c>
+      <c r="P52" s="77" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="Q52" s="77" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="R52" s="81" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="S52" s="80" t="n">
+        <v>0.5599</v>
+      </c>
+      <c r="T52" s="77" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="U52" s="77" t="n">
+        <v>0.6917</v>
+      </c>
+      <c r="V52" s="77" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="W52" s="77" t="n">
+        <v>0.7859</v>
+      </c>
+      <c r="X52" s="77" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="Y52" s="77" t="n">
+        <v>0.8423</v>
+      </c>
+      <c r="Z52" s="81" t="n">
+        <v>0.4836</v>
+      </c>
+      <c r="AA52" s="80" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="AB52" s="80" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="AC52" s="77" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AD52" s="77" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AE52" s="77" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AF52" s="77" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AG52" s="77" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AH52" s="81" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="AI52" s="80" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="AJ52" s="80" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="AK52" s="77" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="AL52" s="77" t="n">
+        <v>0.6616</v>
+      </c>
+      <c r="AM52" s="77" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="AN52" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO52" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="AP52" s="78" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AQ52" s="79" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="76" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="81" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="C53" s="80" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="D53" s="77" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="E53" s="77" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="F53" s="77" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G53" s="77" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="H53" s="77" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I53" s="77" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="J53" s="81" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="K53" s="80" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="L53" s="77" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="M53" s="77" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="N53" s="77" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="O53" s="77" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="P53" s="77" t="n">
+        <v>0.1388</v>
+      </c>
+      <c r="Q53" s="77" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="R53" s="81" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="S53" s="80" t="n">
+        <v>0.5597</v>
+      </c>
+      <c r="T53" s="77" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="U53" s="77" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="V53" s="77" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="W53" s="77" t="n">
+        <v>0.7858000000000001</v>
+      </c>
+      <c r="X53" s="77" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="Y53" s="77" t="n">
+        <v>0.8423</v>
+      </c>
+      <c r="Z53" s="81" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="AA53" s="80" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AB53" s="80" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="AC53" s="77" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AD53" s="77" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AE53" s="77" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AF53" s="77" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AG53" s="77" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="AH53" s="81" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="AI53" s="80" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="AJ53" s="80" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="AK53" s="77" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="AL53" s="77" t="n">
+        <v>0.6616</v>
+      </c>
+      <c r="AM53" s="77" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="AN53" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO53" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="AP53" s="78" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AQ53" s="79" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="76" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="81" t="n">
+        <v>0.5234</v>
+      </c>
+      <c r="C54" s="80" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="D54" s="77" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="E54" s="77" t="n">
+        <v>0.7065</v>
+      </c>
+      <c r="F54" s="77" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="G54" s="77" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="H54" s="77" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="I54" s="77" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="J54" s="81" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="K54" s="80" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="L54" s="77" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="M54" s="77" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="N54" s="77" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="O54" s="77" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="P54" s="77" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="Q54" s="77" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="R54" s="81" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="S54" s="80" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="T54" s="77" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="U54" s="77" t="n">
+        <v>0.6914</v>
+      </c>
+      <c r="V54" s="77" t="n">
+        <v>0.7668</v>
+      </c>
+      <c r="W54" s="77" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="X54" s="77" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="Y54" s="77" t="n">
+        <v>0.8423</v>
+      </c>
+      <c r="Z54" s="81" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AA54" s="80" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AB54" s="80" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AC54" s="77" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AD54" s="77" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AE54" s="77" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AF54" s="77" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AG54" s="77" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="AH54" s="81" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="AI54" s="80" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="AJ54" s="80" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="AK54" s="77" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="AL54" s="77" t="n">
+        <v>0.6615</v>
+      </c>
+      <c r="AM54" s="77" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+      <c r="AN54" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO54" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="AP54" s="78" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AQ54" s="79" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="76" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="81" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="C55" s="80" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="D55" s="77" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="E55" s="77" t="n">
+        <v>0.7064</v>
+      </c>
+      <c r="F55" s="77" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+      <c r="G55" s="77" t="n">
+        <v>0.8082</v>
+      </c>
+      <c r="H55" s="77" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="I55" s="77" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="J55" s="81" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="K55" s="80" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="L55" s="77" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="M55" s="77" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="N55" s="77" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="O55" s="77" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="P55" s="77" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="Q55" s="77" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="R55" s="81" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="S55" s="80" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="T55" s="77" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="U55" s="77" t="n">
+        <v>0.6913</v>
+      </c>
+      <c r="V55" s="77" t="n">
+        <v>0.7668</v>
+      </c>
+      <c r="W55" s="77" t="n">
+        <v>0.7856</v>
+      </c>
+      <c r="X55" s="77" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="Y55" s="77" t="n">
+        <v>0.8423</v>
+      </c>
+      <c r="Z55" s="81" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="AA55" s="80" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="AB55" s="80" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="AC55" s="77" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AD55" s="77" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AE55" s="77" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AF55" s="77" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="AG55" s="77" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="AH55" s="81" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AI55" s="80" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="AJ55" s="80" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AK55" s="77" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="AL55" s="77" t="n">
+        <v>0.6615</v>
+      </c>
+      <c r="AM55" s="77" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+      <c r="AN55" s="77" t="n">
+        <v>0.7186</v>
+      </c>
+      <c r="AO55" s="77" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="AP55" s="78" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AQ55" s="79" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:AS2"/>
+    <mergeCell ref="A1:AS1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" style="28" min="1" max="1"/>
+    <col width="10" customWidth="1" style="28" min="2" max="2"/>
+    <col width="10" customWidth="1" style="28" min="3" max="3"/>
+    <col width="10" customWidth="1" style="28" min="4" max="4"/>
+    <col width="10" customWidth="1" style="28" min="5" max="5"/>
+    <col width="10" customWidth="1" style="28" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>How to Read the Feature Tracking Layer-by-Layer Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="82" t="inlineStr">
+        <is>
+          <t>WHAT ONE CELL MEANS</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="47" t="n"/>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="48" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="83" t="inlineStr">
+        <is>
+          <t>Example: f_sky @ Stage4 = 0.55 at Epoch 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="50">
+        <f> At epoch 25, the blue sky detector at ResNet Stage 4 activates at 0.55 (down from 0.91 at epoch 0, heading toward 0.50 uniform)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>READING LEFT-TO-RIGHT (across layers for ONE feature at ONE epoch)</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="47" t="n"/>
+      <c r="E7" s="47" t="n"/>
+      <c r="F7" s="48" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="84" t="inlineStr">
+        <is>
+          <t>f_sky row, Epoch 25:  Conv1=0.91  Stage1=0.90  Stage2=0.88  Stage3=0.82  Stage4=0.55  FMR=0.51  Post=0.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>Early layers (Conv1): detect edges. Sky edges are still edges. FMR barely changes this (0.91). Gradient is weak here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>Late layers (Stage4, FMR): detect the full sky concept. FMR strongly suppresses this (0.55-&gt;0.51). Gradient is strong here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>RULE: Moving right = closer to FMR = stronger equalization. Moving left = further from FMR = weaker effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>READING TOP-TO-BOTTOM (across epochs for ONE feature at ONE layer)</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="48" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="84" t="inlineStr">
+        <is>
+          <t>f_beak @ Stage4 column: Epoch 0=0.12  E10=0.30  E25=0.42  E50=0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>Epoch 0: Beak detector is QUIET (0.12). ImageNet never needed fine beak shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Epoch 50: Beak detector is BALANCED (0.50). FMR gave it equal prominence. CE loss can now use it for classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>RULE: Moving down = FMR progressing. Useful features rise, irrelevant features drop. Both converge to 0.50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>COMPARING TWO FEATURES SIDE-BY-SIDE</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="47" t="n"/>
+      <c r="E19" s="47" t="n"/>
+      <c r="F19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="inlineStr">
+        <is>
+          <t>At Stage4, Epoch 0:  f_sky=0.91  vs  f_beak=0.12  =  sky is 7.6x LOUDER. Model ignores beak entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="inlineStr">
+        <is>
+          <t>At Stage4, Epoch 25: f_sky=0.55  vs  f_beak=0.42  =  nearly equal now. Model considers both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>At Stage4, Epoch 50: f_sky=0.51  vs  f_beak=0.50  =  perfectly balanced. CE loss picks beak (useful), ignores sky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>COLOR CODING</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="n"/>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="47" t="n"/>
+      <c r="E24" s="47" t="n"/>
+      <c r="F24" s="48" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="85" t="inlineStr">
+        <is>
+          <t>GREEN = near uniform (|f-0.50|&lt;0.03) — FMR fully succeeded here</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="86" t="inlineStr">
+        <is>
+          <t>AMBER = transitioning (0.03&lt;|f-0.50|&lt;0.10) — FMR still working</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="87" t="inlineStr">
+        <is>
+          <t>RED = biased (|f-0.50|&gt;0.10) — FMR incomplete or this is an early layer (gradient attenuated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr">
+        <is>
+          <t>LAYER-BY-LAYER PATTERNS TO WATCH</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="47" t="n"/>
+      <c r="F29" s="48" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>Conv1 column: ALL features barely change (0.87-&gt;0.83). Edge detectors are universal, should not be suppressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>Stage4 column: Features change the MOST. Sky drops (0.91-&gt;0.51). Beak rises (0.12-&gt;0.50). Sweet spot for FMR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>FMR_Applied column: Strongest equalization. All features closest to 0.50. This is FMR directly modifying magnitudes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="50" t="inlineStr">
+        <is>
+          <t>H (entropy) column: Rises 1.8-&gt;7.62 as ALL features become uniform. Watch it climb as epochs advance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="inlineStr">
+        <is>
+          <t>Lambda column: Decays 62-&gt;1 as FMR finishes its job. Strong at first, gentle at the end.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>